--- a/cet4/result/80_科研女神_沙漠探秘的传奇/80_科研女神_沙漠探秘的传奇_学习版.xlsx
+++ b/cet4/result/80_科研女神_沙漠探秘的传奇/80_科研女神_沙漠探秘的传奇_学习版.xlsx
@@ -397,1053 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>desert</v>
       </c>
       <c r="B2" t="str">
-        <v>desert</v>
+        <v>/dɪ'zɜːt; 'dezət/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>沙漠</v>
       </c>
-      <c r="D2" t="str">
-        <v>desert(沙漠)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>stony</v>
       </c>
       <c r="B3" t="str">
-        <v>stony</v>
+        <v>/ˈstoʊni/</v>
       </c>
       <c r="C3" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D3" t="str">
         <v>多石的</v>
       </c>
-      <c r="D3" t="str">
-        <v>stony(多石的)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>scientist</v>
       </c>
       <c r="B4" t="str">
-        <v>scientist</v>
+        <v>/ˈsaɪəntɪst/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>科学家</v>
       </c>
-      <c r="D4" t="str">
-        <v>scientist(科学家)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>commission</v>
       </c>
       <c r="B5" t="str">
-        <v>commission</v>
+        <v>/kəˈmɪʃn/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D5" t="str">
         <v>委托</v>
       </c>
-      <c r="D5" t="str">
-        <v>commission(委托)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>nephew</v>
       </c>
       <c r="B6" t="str">
-        <v>nephew</v>
+        <v>/ˈnefjuː,ˈnevjuː/</v>
       </c>
       <c r="C6" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>侄子</v>
       </c>
-      <c r="D6" t="str">
-        <v>nephew(侄子)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>gift</v>
       </c>
       <c r="B7" t="str">
-        <v>gift</v>
+        <v>/ɡɪft/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D7" t="str">
         <v>天赋</v>
       </c>
-      <c r="D7" t="str">
-        <v>gift(天赋)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>preliminary</v>
       </c>
       <c r="B8" t="str">
-        <v>preliminary</v>
+        <v>/prɪˈlɪmɪneri/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>初步的</v>
       </c>
-      <c r="D8" t="str">
-        <v>preliminary(初步的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>historical</v>
       </c>
       <c r="B9" t="str">
-        <v>historical</v>
+        <v>/hɪˈstɔːrɪkl/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>历史的</v>
       </c>
-      <c r="D9" t="str">
-        <v>historical(历史的)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>dimension</v>
       </c>
       <c r="B10" t="str">
-        <v>dimension</v>
+        <v>/daɪˈmenʃn/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D10" t="str">
         <v>维度</v>
       </c>
-      <c r="D10" t="str">
-        <v>dimension(维度)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>input</v>
       </c>
       <c r="B11" t="str">
-        <v>input</v>
+        <v>/ˈɪnpʊt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>投入</v>
       </c>
-      <c r="D11" t="str">
-        <v>input(投入)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>trail</v>
       </c>
       <c r="B12" t="str">
-        <v>trail</v>
+        <v>/treɪl/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>踪迹</v>
       </c>
-      <c r="D12" t="str">
-        <v>trail(踪迹)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>utmost</v>
       </c>
       <c r="B13" t="str">
-        <v>utmost</v>
+        <v>/ˈʌtmoʊst/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>最大的</v>
       </c>
-      <c r="D13" t="str">
-        <v>utmost(最大的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cloudy</v>
       </c>
       <c r="B14" t="str">
-        <v>cloudy</v>
+        <v>/ˈklaʊdi/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>多云的</v>
       </c>
-      <c r="D14" t="str">
-        <v>cloudy(多云的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>odd</v>
       </c>
       <c r="B15" t="str">
-        <v>odd</v>
+        <v>/ɑːd/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>古怪的</v>
       </c>
-      <c r="D15" t="str">
-        <v>odd(古怪的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>out</v>
       </c>
       <c r="B16" t="str">
-        <v>out</v>
+        <v>/aʊt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi./v./adj./adv./prep.</v>
+      </c>
+      <c r="D16" t="str">
         <v>外面</v>
       </c>
-      <c r="D16" t="str">
-        <v>out(外面)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>healthy</v>
       </c>
       <c r="B17" t="str">
-        <v>healthy</v>
+        <v>/ˈhelθi/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>健康的</v>
       </c>
-      <c r="D17" t="str">
-        <v>healthy(健康的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>outer</v>
       </c>
       <c r="B18" t="str">
-        <v>outer</v>
+        <v>/ˈaʊtər/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>外部的</v>
       </c>
-      <c r="D18" t="str">
-        <v>outer(外部的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>tremendous</v>
       </c>
       <c r="B19" t="str">
-        <v>tremendous</v>
+        <v>/trəˈmendəs/</v>
       </c>
       <c r="C19" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>巨大的</v>
       </c>
-      <c r="D19" t="str">
-        <v>tremendous(巨大的)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>seize</v>
       </c>
       <c r="B20" t="str">
-        <v>seize</v>
+        <v>/siːz/</v>
       </c>
       <c r="C20" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>抓住</v>
       </c>
-      <c r="D20" t="str">
-        <v>seize(抓住)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>abstract</v>
       </c>
       <c r="B21" t="str">
-        <v>abstract</v>
+        <v>/ˈæbstrækt/</v>
       </c>
       <c r="C21" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>抽象的</v>
       </c>
-      <c r="D21" t="str">
-        <v>abstract(抽象的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>attribute</v>
       </c>
       <c r="B22" t="str">
-        <v>attribute</v>
+        <v>/əˈtrɪbjuːt/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D22" t="str">
         <v>属性</v>
       </c>
-      <c r="D22" t="str">
-        <v>attribute(属性)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>crash</v>
       </c>
       <c r="B23" t="str">
-        <v>crash</v>
+        <v>/kræʃ/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D23" t="str">
         <v>碰撞声</v>
       </c>
-      <c r="D23" t="str">
-        <v>crash(碰撞声)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>clumsy</v>
       </c>
       <c r="B24" t="str">
-        <v>clumsy</v>
+        <v>/ˈklʌmzi/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>笨拙的</v>
       </c>
-      <c r="D24" t="str">
-        <v>clumsy(笨拙的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>exclaim</v>
       </c>
       <c r="B25" t="str">
-        <v>exclaim</v>
+        <v>/ɪkˈskleɪm/</v>
       </c>
       <c r="C25" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D25" t="str">
         <v>惊叫</v>
       </c>
-      <c r="D25" t="str">
-        <v>exclaim(惊叫)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>fortunately</v>
       </c>
       <c r="B26" t="str">
-        <v>fortunately</v>
+        <v>/ˈfɔːrtʃənətli/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D26" t="str">
         <v>幸运地</v>
       </c>
-      <c r="D26" t="str">
-        <v>fortunately(幸运地)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>wound</v>
       </c>
       <c r="B27" t="str">
-        <v>wound</v>
+        <v>/wuːnd; waʊnd/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D27" t="str">
         <v>伤口</v>
       </c>
-      <c r="D27" t="str">
-        <v>wound(伤口)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>stage</v>
       </c>
       <c r="B28" t="str">
-        <v>stage</v>
+        <v>/steɪdʒ/</v>
       </c>
       <c r="C28" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D28" t="str">
         <v>上演</v>
       </c>
-      <c r="D28" t="str">
-        <v>stage(上演)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>tame</v>
       </c>
       <c r="B29" t="str">
-        <v>tame</v>
+        <v>/teɪm/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>温顺的</v>
       </c>
-      <c r="D29" t="str">
-        <v>tame(温顺的)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>revolutionary</v>
       </c>
       <c r="B30" t="str">
-        <v>revolutionary</v>
+        <v>/ˌrevəˈluːʃəneri/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D30" t="str">
         <v>革命性的</v>
       </c>
-      <c r="D30" t="str">
-        <v>revolutionary(革命性的)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>zero</v>
       </c>
       <c r="B31" t="str">
-        <v>zero</v>
+        <v>/ˈzɪroʊ,ˈziːroʊ/</v>
       </c>
       <c r="C31" t="str">
+        <v>n./num.</v>
+      </c>
+      <c r="D31" t="str">
         <v>零</v>
       </c>
-      <c r="D31" t="str">
-        <v>zero(零)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>vital</v>
       </c>
       <c r="B32" t="str">
-        <v>vital</v>
+        <v>/ˈvaɪtl/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D32" t="str">
         <v>至关重要的</v>
       </c>
-      <c r="D32" t="str">
-        <v>vital(至关重要的)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>convince</v>
       </c>
       <c r="B33" t="str">
-        <v>convince</v>
+        <v>/kənˈvɪns/</v>
       </c>
       <c r="C33" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D33" t="str">
         <v>说服</v>
       </c>
-      <c r="D33" t="str">
-        <v>convince(说服)📢</v>
-      </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>third</v>
       </c>
       <c r="B34" t="str">
-        <v>third</v>
+        <v>/θɜːrd/</v>
       </c>
       <c r="C34" t="str">
+        <v>num.</v>
+      </c>
+      <c r="D34" t="str">
         <v>第三</v>
       </c>
-      <c r="D34" t="str">
-        <v>third(第三)📢</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>tag</v>
       </c>
       <c r="B35" t="str">
-        <v>tag</v>
+        <v>/tæɡ/</v>
       </c>
       <c r="C35" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D35" t="str">
         <v>标签</v>
       </c>
-      <c r="D35" t="str">
-        <v>tag(标签)📢</v>
-      </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>refuge</v>
       </c>
       <c r="B36" t="str">
-        <v>refuge</v>
+        <v>/ˈrefjuːdʒ/</v>
       </c>
       <c r="C36" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D36" t="str">
         <v>避难所</v>
       </c>
-      <c r="D36" t="str">
-        <v>refuge(避难所)📢</v>
-      </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>hall</v>
       </c>
       <c r="B37" t="str">
-        <v>hall</v>
+        <v>/hɔːl/</v>
       </c>
       <c r="C37" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>大厅</v>
       </c>
-      <c r="D37" t="str">
-        <v>hall(大厅)📢</v>
-      </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>bosom</v>
       </c>
       <c r="B38" t="str">
-        <v>bosom</v>
+        <v>/ˈbʊzəm/</v>
       </c>
       <c r="C38" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D38" t="str">
         <v>胸怀</v>
       </c>
-      <c r="D38" t="str">
-        <v>bosom(胸怀)📢</v>
-      </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>yearly</v>
       </c>
       <c r="B39" t="str">
-        <v>yearly</v>
+        <v>/ˈjɪrli/</v>
       </c>
       <c r="C39" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D39" t="str">
         <v>每年</v>
       </c>
-      <c r="D39" t="str">
-        <v>yearly(每年)📢</v>
-      </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>wit</v>
       </c>
       <c r="B40" t="str">
-        <v>out</v>
+        <v>/wɪt/</v>
       </c>
       <c r="C40" t="str">
-        <v>走出来</v>
+        <v>n./v.</v>
       </c>
       <c r="D40" t="str">
-        <v>out(走出来)📢</v>
+        <v>智慧</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>honesty</v>
       </c>
       <c r="B41" t="str">
-        <v>wit</v>
+        <v>/ˈɑːnəsti/</v>
       </c>
       <c r="C41" t="str">
-        <v>智慧</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>wit(智慧)📢</v>
+        <v>诚实</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>gratitude</v>
       </c>
       <c r="B42" t="str">
-        <v>honesty</v>
+        <v>/ˈɡrætɪtuːd/</v>
       </c>
       <c r="C42" t="str">
-        <v>诚实</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>honesty(诚实)📢</v>
+        <v>感激</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>triumph</v>
       </c>
       <c r="B43" t="str">
-        <v>gratitude</v>
+        <v>/ˈtraɪʌmf/</v>
       </c>
       <c r="C43" t="str">
-        <v>感激</v>
+        <v>n./vi.</v>
       </c>
       <c r="D43" t="str">
-        <v>gratitude(感激)📢</v>
+        <v>胜利</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>rubbish</v>
       </c>
       <c r="B44" t="str">
-        <v>triumph</v>
+        <v>/ˈrʌbɪʃ/</v>
       </c>
       <c r="C44" t="str">
-        <v>胜利</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>triumph(胜利)📢</v>
+        <v>垃圾</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>pot</v>
       </c>
       <c r="B45" t="str">
-        <v>rubbish</v>
+        <v>/pɑːt/</v>
       </c>
       <c r="C45" t="str">
-        <v>垃圾</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>rubbish(垃圾)📢</v>
+        <v>罐子</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>ripen</v>
       </c>
       <c r="B46" t="str">
-        <v>pot</v>
+        <v>/ˈraɪpən/</v>
       </c>
       <c r="C46" t="str">
-        <v>罐子</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>pot(罐子)📢</v>
+        <v>成熟</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>submit</v>
       </c>
       <c r="B47" t="str">
-        <v>stage</v>
+        <v>/səbˈmɪt/</v>
       </c>
       <c r="C47" t="str">
-        <v>阶段</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>stage(阶段)📢</v>
+        <v>提交</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>court</v>
       </c>
       <c r="B48" t="str">
-        <v>attribute</v>
+        <v>/kɔːrt/</v>
       </c>
       <c r="C48" t="str">
-        <v>属性</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>attribute(属性)📢</v>
+        <v>法院</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>fashion</v>
       </c>
       <c r="B49" t="str">
-        <v>ripen</v>
+        <v>/ˈfæʃn/</v>
       </c>
       <c r="C49" t="str">
-        <v>成熟</v>
+        <v>n./vt.</v>
       </c>
       <c r="D49" t="str">
-        <v>ripen(成熟)📢</v>
+        <v>时尚</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>outlet</v>
       </c>
       <c r="B50" t="str">
-        <v>submit</v>
+        <v>/ˈaʊtlet/</v>
       </c>
       <c r="C50" t="str">
-        <v>提交</v>
+        <v>n.</v>
       </c>
       <c r="D50" t="str">
-        <v>submit(提交)📢</v>
+        <v>批发商店</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>police</v>
       </c>
       <c r="B51" t="str">
-        <v>commission</v>
+        <v>/pəˈliːs/</v>
       </c>
       <c r="C51" t="str">
-        <v>委员会</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D51" t="str">
-        <v>commission(委员会)📢</v>
+        <v>警察</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>mist</v>
       </c>
       <c r="B52" t="str">
-        <v>tremendous</v>
+        <v>/mɪst/</v>
       </c>
       <c r="C52" t="str">
-        <v>惊人的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D52" t="str">
-        <v>tremendous(惊人的)📢</v>
+        <v>薄雾</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>displease</v>
       </c>
       <c r="B53" t="str">
-        <v>court</v>
+        <v>/dɪsˈpliːz/</v>
       </c>
       <c r="C53" t="str">
-        <v>法院</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D53" t="str">
-        <v>court(法院)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>court</v>
-      </c>
-      <c r="C54" t="str">
-        <v>法庭</v>
-      </c>
-      <c r="D54" t="str">
-        <v>court(法庭)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>convince</v>
-      </c>
-      <c r="C55" t="str">
-        <v>说服</v>
-      </c>
-      <c r="D55" t="str">
-        <v>convince(说服)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>triumph</v>
-      </c>
-      <c r="C56" t="str">
-        <v>胜利</v>
-      </c>
-      <c r="D56" t="str">
-        <v>triumph(胜利)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>honesty</v>
-      </c>
-      <c r="C57" t="str">
-        <v>诚实</v>
-      </c>
-      <c r="D57" t="str">
-        <v>honesty(诚实)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>fashion</v>
-      </c>
-      <c r="C58" t="str">
-        <v>时尚</v>
-      </c>
-      <c r="D58" t="str">
-        <v>fashion(时尚)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>odd</v>
-      </c>
-      <c r="C59" t="str">
-        <v>奇怪的</v>
-      </c>
-      <c r="D59" t="str">
-        <v>odd(奇怪的)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>outlet</v>
-      </c>
-      <c r="C60" t="str">
-        <v>批发商店</v>
-      </c>
-      <c r="D60" t="str">
-        <v>outlet(批发商店)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>police</v>
-      </c>
-      <c r="C61" t="str">
-        <v>警察</v>
-      </c>
-      <c r="D61" t="str">
-        <v>police(警察)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>seize</v>
-      </c>
-      <c r="C62" t="str">
-        <v>抓住</v>
-      </c>
-      <c r="D62" t="str">
-        <v>seize(抓住)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>exclaim</v>
-      </c>
-      <c r="C63" t="str">
-        <v>呼喊</v>
-      </c>
-      <c r="D63" t="str">
-        <v>exclaim(呼喊)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>wit</v>
-      </c>
-      <c r="C64" t="str">
-        <v>智慧</v>
-      </c>
-      <c r="D64" t="str">
-        <v>wit(智慧)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>mist</v>
-      </c>
-      <c r="C65" t="str">
-        <v>薄雾</v>
-      </c>
-      <c r="D65" t="str">
-        <v>mist(薄雾)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>desert</v>
-      </c>
-      <c r="C66" t="str">
-        <v>沙漠</v>
-      </c>
-      <c r="D66" t="str">
-        <v>desert(沙漠)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>honesty</v>
-      </c>
-      <c r="C67" t="str">
-        <v>诚实</v>
-      </c>
-      <c r="D67" t="str">
-        <v>honesty(诚实)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>displease</v>
-      </c>
-      <c r="C68" t="str">
         <v>使不快</v>
-      </c>
-      <c r="D68" t="str">
-        <v>displease(使不快)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>input</v>
-      </c>
-      <c r="C69" t="str">
-        <v>投入</v>
-      </c>
-      <c r="D69" t="str">
-        <v>input(投入)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>honesty</v>
-      </c>
-      <c r="C70" t="str">
-        <v>诚实</v>
-      </c>
-      <c r="D70" t="str">
-        <v>honesty(诚实)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>yearly</v>
-      </c>
-      <c r="C71" t="str">
-        <v>每年</v>
-      </c>
-      <c r="D71" t="str">
-        <v>yearly(每年)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>triumph</v>
-      </c>
-      <c r="C72" t="str">
-        <v>成功</v>
-      </c>
-      <c r="D72" t="str">
-        <v>triumph(成功)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>honesty</v>
-      </c>
-      <c r="C73" t="str">
-        <v>诚实</v>
-      </c>
-      <c r="D73" t="str">
-        <v>honesty(诚实)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>wit</v>
-      </c>
-      <c r="C74" t="str">
-        <v>智慧</v>
-      </c>
-      <c r="D74" t="str">
-        <v>wit(智慧)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D74"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>